--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1175,7 +1175,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|MedicationStatement)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-strahlentherapie|https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-systemische-therapie|https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-systemische-therapie-medikation)
 </t>
   </si>
   <si>
@@ -1612,7 +1612,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="138.40625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -585,10 +585,36 @@
     <t>AdverseEvent.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>AdverseEvent.extension:ctcaeVersion</t>
+  </si>
+  <si>
+    <t>ctcaeVersion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-ex-onko-nebenwirkung-ctcae-version}
+</t>
+  </si>
+  <si>
+    <t>CTCAE-Version</t>
+  </si>
+  <si>
+    <t>Version des CTCAE-Katalogs nach 15.3 oBDS 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>15.3</t>
   </si>
   <si>
     <t>AdverseEvent.modifierExtension</t>
@@ -739,9 +765,6 @@
     <t>AdverseEvent.event.coding.version</t>
   </si>
   <si>
-    <t>CTCAE-Version</t>
-  </si>
-  <si>
     <t>Version der für Art der Nebenwirkung verwendeten CTCAE-Klassifikation gemäß 15.3 oBDS 2021.</t>
   </si>
   <si>
@@ -749,9 +772,6 @@
   </si>
   <si>
     <t>Coding.version</t>
-  </si>
-  <si>
-    <t>15.3</t>
   </si>
   <si>
     <t>AdverseEvent.event.coding.code</t>
@@ -831,6 +851,12 @@
   </si>
   <si>
     <t>AdverseEvent.event.coding:meddra.version</t>
+  </si>
+  <si>
+    <t>Version des MEDDRA-Katalogs (z. B. 12.0 fuer die von CTCAE v4.03 verwendeten Codes). Die CTCAE-Katalogversion nach oBDS 15.3 steht in der Extension ctcaeVersion.</t>
+  </si>
+  <si>
+    <t>kein oBDS-Feld</t>
   </si>
   <si>
     <t>AdverseEvent.event.coding:meddra.code</t>
@@ -1599,12 +1625,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL88"/>
+  <dimension ref="A1:AL89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.7109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.0703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3380,7 +3406,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3402,14 +3428,12 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3446,19 +3470,17 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3479,48 +3501,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3568,7 +3588,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3577,13 +3597,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
@@ -3591,45 +3611,45 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3678,19 +3698,19 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -3701,10 +3721,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3712,7 +3732,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
@@ -3721,22 +3741,26 @@
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3760,13 +3784,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3784,10 +3808,10 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>84</v>
@@ -3802,15 +3826,15 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3818,22 +3842,22 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>204</v>
@@ -3866,13 +3890,13 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -3890,13 +3914,13 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
@@ -3908,15 +3932,15 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3924,13 +3948,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
@@ -3939,13 +3963,13 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3972,13 +3996,13 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>78</v>
@@ -3996,13 +4020,13 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
@@ -4014,15 +4038,15 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4030,28 +4054,28 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4078,13 +4102,13 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -4102,7 +4126,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4114,32 +4138,32 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4151,17 +4175,15 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4198,31 +4220,31 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4233,14 +4255,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4250,29 +4272,27 @@
         <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>217</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4308,9 +4328,11 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4318,7 +4340,7 @@
         <v>110</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4330,7 +4352,7 @@
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
@@ -4341,10 +4363,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4355,28 +4377,32 @@
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4412,31 +4438,29 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -4447,21 +4471,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4473,17 +4497,15 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4520,31 +4542,31 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4553,48 +4575,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4630,31 +4650,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -4665,10 +4685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4676,7 +4696,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>84</v>
@@ -4691,18 +4711,20 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4750,7 +4772,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4765,7 +4787,7 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
@@ -4773,10 +4795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4799,18 +4821,18 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
         <v>240</v>
       </c>
+      <c r="N30" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -4858,7 +4880,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4873,13 +4895,13 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>243</v>
       </c>
@@ -4898,7 +4920,7 @@
         <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>78</v>
@@ -4907,7 +4929,7 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>244</v>
@@ -4981,7 +5003,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
@@ -4989,10 +5011,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5015,7 +5037,7 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>250</v>
@@ -5023,11 +5045,9 @@
       <c r="M32" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5076,7 +5096,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5097,16 +5117,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5118,7 +5136,7 @@
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -5127,19 +5145,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5164,11 +5182,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5186,13 +5206,13 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
@@ -5207,14 +5227,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5226,25 +5248,29 @@
         <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5268,13 +5294,11 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5292,19 +5316,19 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5315,21 +5339,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5341,17 +5365,15 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5388,31 +5410,31 @@
         <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -5421,48 +5443,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5471,7 +5491,7 @@
         <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>78</v>
@@ -5498,31 +5518,31 @@
         <v>78</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -5533,10 +5553,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5544,7 +5564,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>84</v>
@@ -5559,18 +5579,20 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5579,7 +5601,7 @@
         <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>78</v>
@@ -5618,7 +5640,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5641,10 +5663,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5652,7 +5674,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>84</v>
@@ -5667,18 +5689,18 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
         <v>240</v>
       </c>
+      <c r="N38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5726,7 +5748,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5741,15 +5763,15 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>270</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>243</v>
@@ -5760,13 +5782,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>78</v>
@@ -5775,7 +5797,7 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>244</v>
@@ -5857,10 +5879,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5883,7 +5905,7 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>250</v>
@@ -5891,11 +5913,9 @@
       <c r="M40" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -5944,7 +5964,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5965,16 +5985,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>78</v>
       </c>
@@ -5986,7 +6004,7 @@
         <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>78</v>
@@ -5995,19 +6013,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6056,13 +6074,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6077,14 +6095,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6096,25 +6116,29 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>99</v>
+        <v>276</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6162,19 +6186,19 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -6185,21 +6209,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6211,17 +6235,15 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6258,31 +6280,31 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6291,48 +6313,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6341,7 +6361,7 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>78</v>
@@ -6368,31 +6388,31 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
@@ -6403,10 +6423,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6414,7 +6434,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>84</v>
@@ -6429,18 +6449,20 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -6449,7 +6471,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -6488,7 +6510,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6511,10 +6533,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6522,7 +6544,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>84</v>
@@ -6537,18 +6559,18 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
         <v>240</v>
       </c>
+      <c r="N46" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6596,7 +6618,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6617,9 +6639,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>243</v>
@@ -6630,13 +6652,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -6645,7 +6667,7 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>244</v>
@@ -6727,10 +6749,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6753,7 +6775,7 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>250</v>
@@ -6761,11 +6783,9 @@
       <c r="M48" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -6814,7 +6834,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6835,12 +6855,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6854,7 +6874,7 @@
         <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -6863,19 +6883,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -6924,7 +6944,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6947,18 +6967,18 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>84</v>
@@ -6973,7 +6993,7 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>287</v>
@@ -7034,10 +7054,10 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>84</v>
@@ -7052,7 +7072,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>291</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
@@ -7064,11 +7084,11 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>84</v>
@@ -7083,18 +7103,20 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7145,7 +7167,7 @@
         <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>84</v>
@@ -7160,15 +7182,15 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7182,7 +7204,7 @@
         <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -7191,15 +7213,17 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7248,7 +7272,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7266,15 +7290,15 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7297,13 +7321,13 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7354,7 +7378,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7372,15 +7396,15 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>78</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7403,17 +7427,15 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -7462,7 +7484,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7480,15 +7502,15 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>310</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7499,7 +7521,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -7511,15 +7533,17 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -7568,13 +7592,13 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
@@ -7586,15 +7610,15 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7605,7 +7629,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -7617,13 +7641,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7674,13 +7698,13 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
@@ -7695,12 +7719,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7708,13 +7732,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -7723,13 +7747,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>203</v>
+        <v>324</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7756,11 +7780,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>322</v>
+        <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -7778,7 +7804,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7793,18 +7819,18 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7812,28 +7838,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>99</v>
+        <v>328</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>100</v>
+        <v>329</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7860,13 +7886,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -7884,7 +7908,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>101</v>
+        <v>327</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7896,10 +7920,10 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -7907,21 +7931,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -7933,17 +7957,15 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -7980,31 +8002,31 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8013,16 +8035,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8032,29 +8054,27 @@
         <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>328</v>
+        <v>106</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8090,19 +8110,19 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8114,7 +8134,7 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8123,12 +8143,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8139,28 +8159,32 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>99</v>
+        <v>335</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8208,19 +8232,19 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -8231,21 +8255,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -8257,17 +8281,15 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -8304,31 +8326,31 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -8337,48 +8359,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -8414,31 +8434,31 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -8447,12 +8467,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8460,13 +8480,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
@@ -8475,18 +8495,20 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>333</v>
+        <v>234</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>334</v>
+        <v>235</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -8534,7 +8556,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8555,12 +8577,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8568,13 +8590,13 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
@@ -8583,18 +8605,18 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -8642,7 +8664,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8663,12 +8685,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8676,13 +8698,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
@@ -8691,13 +8713,13 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>244</v>
+        <v>344</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>245</v>
+        <v>345</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
@@ -8773,10 +8795,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8799,7 +8821,7 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>250</v>
@@ -8807,11 +8829,9 @@
       <c r="M67" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -8860,7 +8880,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8881,12 +8901,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8900,7 +8920,7 @@
         <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>78</v>
@@ -8909,19 +8929,19 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -8970,7 +8990,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8991,12 +9011,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9010,7 +9030,7 @@
         <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -9019,16 +9039,20 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>203</v>
+        <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9052,13 +9076,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9076,7 +9100,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9099,10 +9123,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9125,13 +9149,13 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9158,31 +9182,31 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9205,10 +9229,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9231,13 +9255,13 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>352</v>
+        <v>211</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9264,13 +9288,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -9288,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9306,15 +9330,15 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9325,7 +9349,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -9337,13 +9361,13 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9394,13 +9418,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -9412,15 +9436,15 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9428,13 +9452,13 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>78</v>
@@ -9443,13 +9467,13 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9500,7 +9524,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9521,12 +9545,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9534,28 +9558,28 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>98</v>
+        <v>369</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>100</v>
+        <v>371</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9606,19 +9630,19 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>101</v>
+        <v>368</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -9629,21 +9653,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -9655,17 +9679,15 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -9714,19 +9736,19 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -9737,14 +9759,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9757,26 +9779,24 @@
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>368</v>
+        <v>105</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>369</v>
+        <v>106</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O76" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -9824,7 +9844,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9845,44 +9865,48 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -9930,19 +9954,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -9951,26 +9975,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>78</v>
@@ -9979,13 +10003,13 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10036,13 +10060,13 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
@@ -10059,10 +10083,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10073,7 +10097,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -10082,16 +10106,16 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>98</v>
+        <v>369</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>99</v>
+        <v>385</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>100</v>
+        <v>386</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10142,19 +10166,19 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>101</v>
+        <v>384</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -10165,21 +10189,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -10191,17 +10215,15 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -10250,19 +10272,19 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -10273,14 +10295,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10293,26 +10315,24 @@
         <v>78</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>368</v>
+        <v>105</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>369</v>
+        <v>106</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O81" t="s" s="2">
-        <v>187</v>
-      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -10360,7 +10380,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10383,42 +10403,46 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -10442,13 +10466,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -10466,19 +10490,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -10489,10 +10513,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10515,13 +10539,13 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10548,13 +10572,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>394</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -10572,7 +10596,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10595,10 +10619,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10621,13 +10645,13 @@
         <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>391</v>
+        <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10678,7 +10702,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10701,10 +10725,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10727,13 +10751,13 @@
         <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>203</v>
+        <v>399</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10760,31 +10784,31 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10807,10 +10831,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10821,7 +10845,7 @@
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -10833,13 +10857,13 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>400</v>
+        <v>211</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10866,13 +10890,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>78</v>
+        <v>405</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -10890,13 +10914,13 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
@@ -10913,10 +10937,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10939,13 +10963,13 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10996,7 +11020,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11019,10 +11043,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11045,13 +11069,13 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11102,7 +11126,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11123,8 +11147,114 @@
         <v>78</v>
       </c>
     </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL88">
+  <autoFilter ref="A1:AL89">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11134,7 +11264,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-nebenwirkung-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
